--- a/artfynd/A 11984-2024 artfynd.xlsx
+++ b/artfynd/A 11984-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115397504</v>
+        <v>115397446</v>
       </c>
       <c r="B2" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478235</v>
+        <v>478124</v>
       </c>
       <c r="R2" t="n">
-        <v>7087205</v>
+        <v>7087126</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,19 +776,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115397484</v>
+        <v>115397458</v>
       </c>
       <c r="B3" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -824,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478223</v>
+        <v>478124</v>
       </c>
       <c r="R3" t="n">
-        <v>7087196</v>
+        <v>7087126</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,6 +874,107 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>115397484</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Tjärnafjällsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>478223</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7087196</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-03-15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-03-15</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11984-2024 artfynd.xlsx
+++ b/artfynd/A 11984-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115397446</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115397458</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,8 +990,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115397484</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>